--- a/ExcelRAddIn/Tests/Data Wrangling.xlsx
+++ b/ExcelRAddIn/Tests/Data Wrangling.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\Projects\C#\Office\ExcelRAddIn\Tests\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\Projects\C#\Office\Office365 AddIns\ExcelRAddIn\Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D656A1E-514F-4F94-8698-6BCC3D91988B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B8A0B7-CFEC-4701-904D-AC6814005ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{5003AA1E-52FB-411B-9B31-43F0075F6D84}"/>
   </bookViews>
@@ -116,14 +116,6 @@
   </si>
   <si>
     <t>plot(ggplot(data = movies_data, aes(x = Year, y = no_employees)) +
-  geom_point(aes(colour = Country)) +
-  labs(x = "Years", 
-       y = "Number of employees",
-       colour = "Country") +
-  theme_bw())</t>
-  </si>
-  <si>
-    <t>plot(ggplot(data = movies_data, aes(x = Year, y = no_employees)) +
   geom_point() +
   facet_wrap(~Country, ncol = 4) +
   labs(x = "Years", 
@@ -205,6 +197,14 @@
   </si>
   <si>
     <t>movie_data &lt;- read_csv('https://jumpingrivers.com/blog/comparing-r-excel-data-wrangling/blog-data.csv')</t>
+  </si>
+  <si>
+    <t>plot(ggplot(data = movies_data, aes(x = year, y = no_employees)) +
+  geom_point(aes(colour = country)) +
+  labs(x = "Years", 
+       y = "Number of employees",
+       colour = "country") +
+  theme_bw())</t>
   </si>
 </sst>
 </file>
@@ -278,16 +278,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>480060</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>670560</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>91440</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>541020</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>335280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -317,7 +317,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="6629400" y="853440"/>
+          <a:off x="6850380" y="1676400"/>
           <a:ext cx="4328160" cy="4328160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -463,9 +463,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -503,7 +503,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -609,7 +609,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -751,7 +751,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -777,200 +777,37 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9F63317-D946-4322-9CB8-4E6BA5495368}">
-  <dimension ref="B2:D38"/>
+  <dimension ref="B2:D4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>1</v>
       </c>
       <c r="D2" t="str" cm="1">
-        <f t="array" ref="D2:D18">_xll.RScript.Evaluate(B2)</f>
-        <v>lubridate</v>
+        <f t="array" ref="D2">_xll.RScript.Evaluate(B2, TRUE)</f>
+        <v>OK</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D3" t="str">
-        <v>forcats</v>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="str" cm="1">
+        <f t="array" ref="D3">_xll.RScript.Evaluate(B3, TRUE)</f>
+        <v>OK</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D4" t="str">
-        <v>stringr</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D5" t="str">
-        <v>dplyr</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D6" t="str">
-        <v>purrr</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D7" t="str">
-        <v>readr</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D8" t="str">
-        <v>tidyr</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D9" t="str">
-        <v>tibble</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D10" t="str">
-        <v>ggplot2</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D11" t="str">
-        <v>tidyverse</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D12" t="str">
-        <v>stats</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D13" t="str">
-        <v>graphics</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D14" t="str">
-        <v>grDevices</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D15" t="str">
-        <v>utils</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D16" t="str">
-        <v>datasets</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D17" t="str">
-        <v>methods</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D18" t="str">
-        <v>base</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B19" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" t="str" cm="1">
-        <f t="array" ref="D20:D38">_xll.RScript.Evaluate(B20)</f>
-        <v>viridis</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D21" t="str">
-        <v>viridisLite</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D22" t="str">
-        <v>lubridate</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D23" t="str">
-        <v>forcats</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D24" t="str">
-        <v>stringr</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D25" t="str">
-        <v>dplyr</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D26" t="str">
-        <v>purrr</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D27" t="str">
-        <v>readr</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D28" t="str">
-        <v>tidyr</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D29" t="str">
-        <v>tibble</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D30" t="str">
-        <v>ggplot2</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D31" t="str">
-        <v>tidyverse</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D32" t="str">
-        <v>stats</v>
-      </c>
-    </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D33" t="str">
-        <v>graphics</v>
-      </c>
-    </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D34" t="str">
-        <v>grDevices</v>
-      </c>
-    </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D35" t="str">
-        <v>utils</v>
-      </c>
-    </row>
-    <row r="36" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D36" t="str">
-        <v>datasets</v>
-      </c>
-    </row>
-    <row r="37" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D37" t="str">
-        <v>methods</v>
-      </c>
-    </row>
-    <row r="38" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D38" t="str">
-        <v>base</v>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="str" cm="1">
+        <f t="array" ref="D4">_xll.RScript.Evaluate(B4, TRUE)</f>
+        <v>OK</v>
       </c>
     </row>
   </sheetData>
@@ -3351,56 +3188,16 @@
   <sheetData>
     <row r="2" spans="2:3" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C2" t="str" cm="1">
-        <f t="array" ref="C2:C10">_xll.RScript.Evaluate(B2)</f>
-        <v>data</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C3" t="str">
-        <v>layers</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C4" t="str">
-        <v>scales</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C5" t="str">
-        <v>mapping</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C6" t="str">
-        <v>theme</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C7" t="str">
-        <v>coordinates</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C8" t="str">
-        <v>facet</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C9" t="str">
-        <v>plot_env</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C10" t="str">
-        <v>labels</v>
+        <f t="array" ref="C2">_xll.RScript.Evaluate(B2, TRUE)</f>
+        <v>OK</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C27" t="str" cm="1">
         <f t="array" ref="C27:C35">_xll.RScript.Evaluate(B27)</f>
@@ -3449,7 +3246,7 @@
     </row>
     <row r="45" spans="2:3" ht="129.6" x14ac:dyDescent="0.3">
       <c r="B45" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C45" t="str" cm="1">
         <f t="array" ref="C45:C53">_xll.RScript.Evaluate(B45)</f>
@@ -3513,13 +3310,13 @@
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
@@ -3536,7 +3333,7 @@
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" t="str" cm="1">
         <f t="array" ref="C6">_xll.RScript.Evaluate(B6)</f>
@@ -3545,7 +3342,7 @@
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" t="str" cm="1">
         <f t="array" ref="C7">_xll.RScript.Evaluate(B7)</f>
@@ -3554,7 +3351,7 @@
     </row>
     <row r="9" spans="2:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9" t="str" cm="1">
         <f t="array" ref="C9">_xll.RScript.Evaluate(B9)</f>
@@ -3563,7 +3360,7 @@
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" cm="1">
         <f t="array" ref="C11">_xll.RScript.Evaluate(B11)</f>
@@ -3572,7 +3369,7 @@
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13" t="str" cm="1">
         <f t="array" ref="C13">_xll.RScript.Evaluate(B13)</f>
@@ -3581,7 +3378,7 @@
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" t="str" cm="1">
         <f t="array" ref="C14">_xll.RScript.Evaluate(B14)</f>
@@ -3590,7 +3387,7 @@
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C15" t="str" cm="1">
         <f t="array" ref="C15">_xll.RScript.Evaluate(B15)</f>
@@ -3599,7 +3396,7 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" t="str" cm="1">
         <f t="array" ref="C17">_xll.RScript.Evaluate(B17)</f>
@@ -3608,7 +3405,7 @@
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C18" cm="1">
         <f t="array" ref="C18">_xll.RScript.Evaluate(B18)</f>
@@ -3617,7 +3414,7 @@
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" cm="1">
         <f t="array" ref="C19">_xll.RScript.Evaluate(B19)</f>
@@ -3626,7 +3423,7 @@
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20" cm="1">
         <f t="array" ref="C20">_xll.RScript.Evaluate(B20)</f>
@@ -3635,7 +3432,7 @@
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C23" t="str" cm="1">
         <f t="array" ref="C23">_xll.RScript.Evaluate(B23)</f>
@@ -3645,7 +3442,7 @@
     </row>
     <row r="26" spans="2:3" ht="72" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26" t="str" cm="1">
         <f t="array" ref="C26">_xll.RScript.Evaluate(B26)</f>
@@ -3655,7 +3452,7 @@
     </row>
     <row r="28" spans="2:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" t="str" cm="1">
         <f t="array" ref="C28">_xll.RScript.Evaluate(B28)</f>
@@ -3665,7 +3462,7 @@
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C31" t="str" cm="1">
         <f t="array" ref="C31">_xll.RScript.Evaluate(B31)</f>
